--- a/data/trans_bre/IP16B03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B03-Clase-trans_bre.xlsx
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,86</t>
+          <t>0,0; 32,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,29</t>
+          <t>0,0; 48,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B03-Clase-trans_bre.xlsx
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,77</t>
+          <t>0,0; 32,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,75</t>
+          <t>0,0; 48,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
